--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run4/epoch_40/per_file_predictions_epoch_40.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run4/epoch_40/per_file_predictions_epoch_40.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="515">
   <si>
     <t>Filename</t>
   </si>
@@ -808,760 +808,757 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9083,0.0104,0.0219,0.0058</t>
-  </si>
-  <si>
-    <t>0.0011,0.0018,0.0003,0.9991</t>
-  </si>
-  <si>
-    <t>0.9792,0.0015,0.0009,0.0037</t>
-  </si>
-  <si>
-    <t>0.0525,0.0022,0.0003,0.9620</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9987,0.0010,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9982,0.0010,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9931,0.0078,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9944,0.0075,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9989,0.0005,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.2482,0.7862,0.0035,0.0004</t>
-  </si>
-  <si>
-    <t>0.0121,0.0034,0.9865,0.0006</t>
-  </si>
-  <si>
-    <t>0.8046,0.0044,0.2044,0.0010</t>
-  </si>
-  <si>
-    <t>0.2006,0.0281,0.6599,0.0090</t>
-  </si>
-  <si>
-    <t>0.6830,0.0439,0.1974,0.0054</t>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.8461,0.0195,0.0487,0.0216</t>
+  </si>
+  <si>
+    <t>0.0006,0.0019,0.0001,0.9996</t>
+  </si>
+  <si>
+    <t>0.9838,0.0020,0.0007,0.0018</t>
+  </si>
+  <si>
+    <t>0.0107,0.0030,0.0006,0.9927</t>
+  </si>
+  <si>
+    <t>0.9991,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0007,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9966,0.0020,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9960,0.0037,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9978,0.0023,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.7850,0.1037,0.0332,0.0007</t>
+  </si>
+  <si>
+    <t>0.0121,0.0142,0.9772,0.0008</t>
+  </si>
+  <si>
+    <t>0.6644,0.0046,0.3590,0.0007</t>
+  </si>
+  <si>
+    <t>0.0056,0.0100,0.9888,0.0006</t>
+  </si>
+  <si>
+    <t>0.5337,0.0870,0.1852,0.0025</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0013,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0011,0.0000</t>
+  </si>
+  <si>
+    <t>0.0211,0.9814,0.0017,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0012,0.0000</t>
+  </si>
+  <si>
+    <t>0.1980,0.1010,0.3602,0.0096</t>
+  </si>
+  <si>
+    <t>0.3783,0.0164,0.5372,0.0045</t>
+  </si>
+  <si>
+    <t>0.0199,0.0128,0.9591,0.0034</t>
+  </si>
+  <si>
+    <t>0.0331,0.0284,0.9228,0.0023</t>
+  </si>
+  <si>
+    <t>0.0035,0.0013,0.9938,0.0009</t>
+  </si>
+  <si>
+    <t>0.0102,0.0013,0.9878,0.0004</t>
+  </si>
+  <si>
+    <t>0.0015,0.0021,0.9978,0.0002</t>
+  </si>
+  <si>
+    <t>0.0716,0.9377,0.0052,0.0005</t>
+  </si>
+  <si>
+    <t>0.6610,0.3921,0.0060,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,0.9998,0.0054</t>
+  </si>
+  <si>
+    <t>0.0002,0.9996,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.9793,0.0102,0.0023,0.0002</t>
+  </si>
+  <si>
+    <t>0.9306,0.0554,0.0030,0.0001</t>
+  </si>
+  <si>
+    <t>0.3734,0.7095,0.0034,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.9974,0.0108,0.0000</t>
+  </si>
+  <si>
+    <t>0.0098,0.4066,0.7549,0.0008</t>
+  </si>
+  <si>
+    <t>0.7710,0.0014,0.2732,0.0003</t>
+  </si>
+  <si>
+    <t>0.0097,0.5321,0.7973,0.0017</t>
+  </si>
+  <si>
+    <t>0.0096,0.0019,0.9829,0.0024</t>
+  </si>
+  <si>
+    <t>0.0226,0.0237,0.9570,0.0006</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0034,0.9991,0.0005</t>
+  </si>
+  <si>
+    <t>0.0002,0.9026,0.0001,0.9091</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0010,0.0025</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0024,0.0000</t>
   </si>
   <si>
     <t>0.0000,1.0000,0.0003,0.0000</t>
   </si>
   <si>
-    <t>0.0000,0.9999,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0086,0.9907,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.7731,0.0112,0.1550,0.0019</t>
-  </si>
-  <si>
-    <t>0.5862,0.0758,0.1550,0.0028</t>
-  </si>
-  <si>
-    <t>0.0055,0.0244,0.9839,0.0025</t>
-  </si>
-  <si>
-    <t>0.0496,0.0645,0.8092,0.0029</t>
-  </si>
-  <si>
-    <t>0.0042,0.0013,0.9932,0.0005</t>
-  </si>
-  <si>
-    <t>0.0044,0.0015,0.9922,0.0004</t>
-  </si>
-  <si>
-    <t>0.0007,0.0008,0.9990,0.0001</t>
-  </si>
-  <si>
-    <t>0.0303,0.9696,0.0030,0.0009</t>
-  </si>
-  <si>
-    <t>0.6110,0.3065,0.0218,0.0008</t>
-  </si>
-  <si>
-    <t>0.0000,0.0006,0.9996,0.0048</t>
-  </si>
-  <si>
-    <t>0.0056,0.9779,0.0375,0.0004</t>
-  </si>
-  <si>
-    <t>0.9251,0.0465,0.0099,0.0006</t>
-  </si>
-  <si>
-    <t>0.9616,0.0313,0.0022,0.0001</t>
-  </si>
-  <si>
-    <t>0.0927,0.9292,0.0031,0.0001</t>
-  </si>
-  <si>
-    <t>0.0025,0.9958,0.0043,0.0000</t>
-  </si>
-  <si>
-    <t>0.0136,0.6751,0.3536,0.0007</t>
-  </si>
-  <si>
-    <t>0.0125,0.0219,0.9715,0.0011</t>
-  </si>
-  <si>
-    <t>0.0028,0.2845,0.9746,0.0007</t>
-  </si>
-  <si>
-    <t>0.0122,0.0052,0.9738,0.0027</t>
-  </si>
-  <si>
-    <t>0.0004,0.0396,0.9982,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0064,0.0009,0.9859,0.0032</t>
-  </si>
-  <si>
-    <t>0.0001,0.9809,0.0001,0.5892</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0023,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0099,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.2204,0.9824,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.6107,0.9901,0.0001</t>
-  </si>
-  <si>
-    <t>0.0329,0.0044,0.9519,0.0017</t>
-  </si>
-  <si>
-    <t>0.0101,0.0005,0.9896,0.0004</t>
-  </si>
-  <si>
-    <t>0.0009,0.0044,0.9979,0.0003</t>
-  </si>
-  <si>
-    <t>0.0032,0.0032,0.9911,0.0031</t>
-  </si>
-  <si>
-    <t>0.9930,0.0073,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9957,0.0015,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9977,0.0014,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0005,0.9997,0.0009</t>
-  </si>
-  <si>
-    <t>0.9970,0.0016,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9942,0.0078,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9777,0.0251,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9894,0.9407,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.0078,0.9965,0.0002</t>
-  </si>
-  <si>
-    <t>0.0061,0.0104,0.9895,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9996,0.9918,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.9992,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9998,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9718,0.0048,0.0125,0.0004</t>
-  </si>
-  <si>
-    <t>0.8978,0.0410,0.0248,0.0009</t>
-  </si>
-  <si>
-    <t>0.0004,0.0025,0.9995,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.9978,0.9694,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9908,0.8926,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9992,0.0114,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9985,0.4842,0.0000</t>
-  </si>
-  <si>
-    <t>0.0055,0.0017,0.0017,0.9951</t>
-  </si>
-  <si>
-    <t>0.0008,0.0006,0.0003,0.9995</t>
-  </si>
-  <si>
-    <t>0.0007,0.0097,0.0002,0.9992</t>
-  </si>
-  <si>
-    <t>0.0003,0.0004,0.0001,0.9997</t>
-  </si>
-  <si>
-    <t>0.0009,0.0002,0.0002,0.9995</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.8632,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9772,0.9554,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9974,0.7384,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9985,0.5427,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.3858,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9985,0.9887,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9905,0.0113,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9686,0.0589,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9839,0.0143,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9949,0.0061,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9902,0.0126,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9857,0.0247,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0005,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9974,0.0021,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9980,0.0015,0.0000,0.0000</t>
+    <t>0.0000,0.2891,0.9972,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.4001,0.9967,0.0001</t>
+  </si>
+  <si>
+    <t>0.0044,0.0051,0.9888,0.0027</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9995,0.0004</t>
+  </si>
+  <si>
+    <t>0.0030,0.0007,0.9965,0.0002</t>
+  </si>
+  <si>
+    <t>0.0076,0.0251,0.9579,0.0056</t>
+  </si>
+  <si>
+    <t>0.9822,0.0288,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9975,0.0009,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9973,0.0015,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0011,0.9997,0.0004</t>
+  </si>
+  <si>
+    <t>0.9945,0.0042,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9969,0.0034,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9942,0.0044,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9888,0.9663,0.0000</t>
+  </si>
+  <si>
+    <t>0.0019,0.0599,0.9852,0.0003</t>
+  </si>
+  <si>
+    <t>0.0065,0.0178,0.9852,0.0013</t>
+  </si>
+  <si>
+    <t>0.0000,0.9993,0.9898,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9994,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9106,0.0058,0.0596,0.0025</t>
+  </si>
+  <si>
+    <t>0.8064,0.0366,0.0802,0.0015</t>
+  </si>
+  <si>
+    <t>0.0003,0.0034,0.9996,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.9862,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9986,0.3417,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0017,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.6482,0.0000</t>
+  </si>
+  <si>
+    <t>0.0093,0.0011,0.0042,0.9919</t>
+  </si>
+  <si>
+    <t>0.0000,0.0012,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0016,0.0002,0.9996</t>
+  </si>
+  <si>
+    <t>0.0065,0.0058,0.0000,0.9860</t>
+  </si>
+  <si>
+    <t>0.0007,0.0001,0.0007,0.9993</t>
+  </si>
+  <si>
+    <t>0.0000,0.0007,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.8635,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9912,0.8384,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9984,0.8902,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9991,0.0455,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9991,0.6197,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9950,0.9796,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0011,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9884,0.0124,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9947,0.0075,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9968,0.0018,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9948,0.0035,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9982,0.0010,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9917,0.0072,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9918,0.0080,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0008,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9984,0.0005,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0017,0.0101,0.9950,0.0012</t>
+  </si>
+  <si>
+    <t>0.9800,0.0027,0.0039,0.0002</t>
+  </si>
+  <si>
+    <t>0.0024,0.0015,0.9970,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.9991,0.0124,0.0000</t>
+  </si>
+  <si>
+    <t>0.0015,0.9978,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.9982,0.0022,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.9997,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0023,0.0000</t>
+  </si>
+  <si>
+    <t>0.0433,0.9656,0.0020,0.0002</t>
+  </si>
+  <si>
+    <t>0.0397,0.9061,0.0374,0.0217</t>
+  </si>
+  <si>
+    <t>0.0274,0.0263,0.9433,0.0064</t>
+  </si>
+  <si>
+    <t>0.1588,0.8064,0.0147,0.0030</t>
+  </si>
+  <si>
+    <t>0.4847,0.0962,0.2228,0.0086</t>
+  </si>
+  <si>
+    <t>0.0301,0.0196,0.0342,0.9412</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9979,0.8814,0.0000</t>
+  </si>
+  <si>
+    <t>0.0014,0.9972,0.0082,0.0000</t>
+  </si>
+  <si>
+    <t>0.6394,0.4693,0.0042,0.0001</t>
+  </si>
+  <si>
+    <t>0.7368,0.3110,0.0063,0.0001</t>
+  </si>
+  <si>
+    <t>0.9969,0.0014,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9968,0.0021,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9981,0.0010,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9965,0.0007,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9969,0.0020,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9893,0.0049,0.0017,0.0001</t>
+  </si>
+  <si>
+    <t>0.9980,0.0007,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0003,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9723,0.9900,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.9108,0.9216,0.0000</t>
+  </si>
+  <si>
+    <t>0.0025,0.0563,0.9841,0.0004</t>
+  </si>
+  <si>
+    <t>0.0049,0.4506,0.7348,0.0002</t>
+  </si>
+  <si>
+    <t>0.9674,0.0109,0.0032,0.0003</t>
+  </si>
+  <si>
+    <t>0.9462,0.0226,0.0068,0.0009</t>
+  </si>
+  <si>
+    <t>0.0092,0.0014,0.9867,0.0024</t>
+  </si>
+  <si>
+    <t>0.2114,0.6479,0.0162,0.0267</t>
+  </si>
+  <si>
+    <t>0.1389,0.0026,0.0001,0.7663</t>
+  </si>
+  <si>
+    <t>0.0000,0.0013,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.3867,0.0000,0.9996</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.0001,0.9998</t>
+  </si>
+  <si>
+    <t>0.0000,0.9992,0.9904,0.0000</t>
+  </si>
+  <si>
+    <t>0.9975,0.0014,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0126,0.9865,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.9951,0.0015,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.2730,0.8095,0.0025,0.0001</t>
+  </si>
+  <si>
+    <t>0.9979,0.0002,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9533,0.0011,0.0010,0.0178</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0028,0.0864,0.9917,0.0016</t>
+  </si>
+  <si>
+    <t>0.9222,0.0004,0.0137,0.0204</t>
+  </si>
+  <si>
+    <t>0.9912,0.0015,0.0015,0.0005</t>
+  </si>
+  <si>
+    <t>0.3667,0.6919,0.0042,0.0008</t>
+  </si>
+  <si>
+    <t>0.9348,0.0437,0.0080,0.0012</t>
+  </si>
+  <si>
+    <t>0.9108,0.0596,0.0095,0.0011</t>
+  </si>
+  <si>
+    <t>0.0206,0.9711,0.0009,0.0019</t>
+  </si>
+  <si>
+    <t>0.1392,0.8375,0.0216,0.0043</t>
+  </si>
+  <si>
+    <t>0.3766,0.6418,0.0163,0.0021</t>
   </si>
   <si>
     <t>0.9977,0.0009,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.0006,0.0008,0.9990,0.0001</t>
-  </si>
-  <si>
-    <t>0.0100,0.0374,0.9724,0.0046</t>
-  </si>
-  <si>
-    <t>0.9889,0.0017,0.0018,0.0001</t>
-  </si>
-  <si>
-    <t>0.0029,0.0019,0.9965,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.9993,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9995,0.0044,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.9987,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9994,0.0052,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9997,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9997,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.0404,0.9659,0.0019,0.0002</t>
-  </si>
-  <si>
-    <t>0.6789,0.1421,0.0391,0.0226</t>
-  </si>
-  <si>
-    <t>0.0942,0.0466,0.8202,0.0047</t>
-  </si>
-  <si>
-    <t>0.0176,0.9722,0.0037,0.0029</t>
-  </si>
-  <si>
-    <t>0.4581,0.4182,0.0236,0.0007</t>
-  </si>
-  <si>
-    <t>0.0010,0.3300,0.0015,0.9857</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0646,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0006,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,0.9972,0.8949,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9995,0.0039,0.0000</t>
-  </si>
-  <si>
-    <t>0.5900,0.5253,0.0033,0.0001</t>
-  </si>
-  <si>
-    <t>0.5074,0.5967,0.0041,0.0001</t>
-  </si>
-  <si>
-    <t>0.9978,0.0009,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9964,0.0028,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9977,0.0012,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9965,0.0015,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9968,0.0012,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9986,0.0005,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9660,0.9981,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.4442,0.9979,0.0000</t>
-  </si>
-  <si>
-    <t>0.0072,0.1123,0.9605,0.0003</t>
-  </si>
-  <si>
-    <t>0.0034,0.1932,0.9369,0.0011</t>
-  </si>
-  <si>
-    <t>0.9732,0.0048,0.0044,0.0004</t>
-  </si>
-  <si>
-    <t>0.3700,0.0202,0.5561,0.0113</t>
-  </si>
-  <si>
-    <t>0.0738,0.0052,0.9193,0.0036</t>
-  </si>
-  <si>
-    <t>0.6462,0.0495,0.2298,0.0072</t>
-  </si>
-  <si>
-    <t>0.2287,0.0054,0.0000,0.4007</t>
-  </si>
-  <si>
-    <t>0.0000,0.0020,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0176,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9970,0.9787,0.0000</t>
-  </si>
-  <si>
-    <t>0.9970,0.0013,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0541,0.9533,0.0014,0.0006</t>
-  </si>
-  <si>
-    <t>0.9961,0.0014,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.3548,0.7064,0.0063,0.0002</t>
-  </si>
-  <si>
-    <t>0.9970,0.0004,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0106,0.0002,0.0004,0.9965</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0026,0.1220,0.9891,0.0011</t>
-  </si>
-  <si>
-    <t>0.9900,0.0009,0.0021,0.0007</t>
-  </si>
-  <si>
-    <t>0.9857,0.0048,0.0018,0.0009</t>
-  </si>
-  <si>
-    <t>0.0427,0.9550,0.0059,0.0006</t>
-  </si>
-  <si>
-    <t>0.9662,0.0212,0.0042,0.0006</t>
-  </si>
-  <si>
-    <t>0.9699,0.0220,0.0020,0.0002</t>
-  </si>
-  <si>
-    <t>0.0072,0.9905,0.0005,0.0005</t>
-  </si>
-  <si>
-    <t>0.3460,0.4666,0.0617,0.0316</t>
-  </si>
-  <si>
-    <t>0.0555,0.9374,0.0047,0.0037</t>
-  </si>
-  <si>
-    <t>0.9985,0.0005,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0007,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9963,0.0021,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9969,0.0005,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9975,0.0009,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9953,0.0027,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.5779,0.5501,0.0009,0.0002</t>
-  </si>
-  <si>
-    <t>0.7613,0.3206,0.0025,0.0001</t>
-  </si>
-  <si>
-    <t>0.7721,0.3080,0.0041,0.0002</t>
-  </si>
-  <si>
-    <t>0.9609,0.0329,0.0036,0.0007</t>
-  </si>
-  <si>
-    <t>0.0221,0.9831,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9817,0.0127,0.0011,0.0004</t>
-  </si>
-  <si>
-    <t>0.9759,0.0193,0.0020,0.0003</t>
-  </si>
-  <si>
-    <t>0.8942,0.1269,0.0008,0.0007</t>
-  </si>
-  <si>
-    <t>0.0000,0.0007,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.8909,0.0885,0.0137,0.0016</t>
-  </si>
-  <si>
-    <t>0.0003,0.0407,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.3658,0.9973,0.0005</t>
-  </si>
-  <si>
-    <t>0.0004,0.0028,0.9989,0.0006</t>
-  </si>
-  <si>
-    <t>0.0569,0.0226,0.9032,0.0014</t>
-  </si>
-  <si>
-    <t>0.0003,0.0040,0.9991,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0107,0.9991,0.0002</t>
-  </si>
-  <si>
-    <t>0.0331,0.0434,0.9189,0.0078</t>
-  </si>
-  <si>
-    <t>0.0113,0.0029,0.9867,0.0005</t>
-  </si>
-  <si>
-    <t>0.6354,0.1292,0.0994,0.0051</t>
-  </si>
-  <si>
-    <t>0.1022,0.5993,0.1532,0.0022</t>
-  </si>
-  <si>
-    <t>0.1091,0.4920,0.1736,0.0010</t>
-  </si>
-  <si>
-    <t>0.2643,0.5704,0.0351,0.0009</t>
-  </si>
-  <si>
-    <t>0.7266,0.0430,0.1028,0.0157</t>
-  </si>
-  <si>
-    <t>0.0946,0.3478,0.2389,0.0163</t>
-  </si>
-  <si>
-    <t>0.0027,0.9967,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.0038,0.9953,0.0044,0.0000</t>
-  </si>
-  <si>
-    <t>0.1317,0.9231,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.8666,0.2030,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.0478,0.9718,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.1150,0.8381,0.0058,0.0099</t>
-  </si>
-  <si>
-    <t>0.9415,0.0221,0.0122,0.0006</t>
-  </si>
-  <si>
-    <t>0.8322,0.0498,0.0048,0.0052</t>
-  </si>
-  <si>
-    <t>0.0034,0.9919,0.0010,0.0051</t>
-  </si>
-  <si>
-    <t>0.8307,0.0062,0.1499,0.0014</t>
-  </si>
-  <si>
-    <t>0.0177,0.0013,0.9768,0.0036</t>
-  </si>
-  <si>
-    <t>0.0070,0.0251,0.9756,0.0005</t>
-  </si>
-  <si>
-    <t>0.0012,0.5806,0.9813,0.0004</t>
-  </si>
-  <si>
-    <t>0.6850,0.0034,0.3173,0.0003</t>
-  </si>
-  <si>
-    <t>0.0014,0.5274,0.9492,0.0002</t>
-  </si>
-  <si>
-    <t>0.9976,0.0019,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9567,0.0606,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9455,0.0806,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9814,0.0259,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9868,0.0170,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9763,0.0244,0.0011,0.0002</t>
-  </si>
-  <si>
-    <t>0.9972,0.0011,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9981,0.0005,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0012,0.0039,0.9977,0.0008</t>
-  </si>
-  <si>
-    <t>0.1059,0.7990,0.0388,0.0051</t>
-  </si>
-  <si>
-    <t>0.8850,0.0020,0.0698,0.0032</t>
-  </si>
-  <si>
-    <t>0.0000,0.0011,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0014,0.0005,0.9979,0.0002</t>
-  </si>
-  <si>
-    <t>0.0248,0.1233,0.8314,0.0018</t>
-  </si>
-  <si>
-    <t>0.0009,0.0031,0.9973,0.0003</t>
-  </si>
-  <si>
-    <t>0.0003,0.0010,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0030,0.0022,0.9939,0.0002</t>
-  </si>
-  <si>
-    <t>0.0022,0.0335,0.9916,0.0015</t>
-  </si>
-  <si>
-    <t>0.8421,0.0185,0.0774,0.0012</t>
-  </si>
-  <si>
-    <t>0.9315,0.0013,0.0695,0.0006</t>
-  </si>
-  <si>
-    <t>0.9745,0.0170,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9913,0.0121,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9982,0.0019,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9977,0.0021,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9894,0.0082,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0006,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9962,0.0031,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9930,0.0073,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9969,0.0016,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0088,0.5334,0.7785,0.0007</t>
-  </si>
-  <si>
-    <t>0.0010,0.0015,0.9988,0.0000</t>
-  </si>
-  <si>
-    <t>0.0012,0.3690,0.9606,0.0003</t>
-  </si>
-  <si>
-    <t>0.0062,0.8995,0.2483,0.0027</t>
-  </si>
-  <si>
-    <t>0.0002,0.0018,0.9992,0.0006</t>
-  </si>
-  <si>
-    <t>0.3531,0.0049,0.5877,0.0266</t>
-  </si>
-  <si>
-    <t>0.0046,0.0008,0.9863,0.0072</t>
-  </si>
-  <si>
-    <t>0.0062,0.0031,0.9887,0.0009</t>
-  </si>
-  <si>
-    <t>0.5490,0.0005,0.0037,0.5193</t>
-  </si>
-  <si>
-    <t>0.0006,0.4255,0.0004,0.9960</t>
-  </si>
-  <si>
-    <t>0.0006,0.0004,0.0003,0.9996</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.8754,0.0418,0.0029,0.0101</t>
+    <t>0.9981,0.0012,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9970,0.0012,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9975,0.0004,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9942,0.0026,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9976,0.0015,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9982,0.0012,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.4952,0.6281,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.7041,0.4071,0.0022,0.0001</t>
+  </si>
+  <si>
+    <t>0.5245,0.6003,0.0027,0.0001</t>
+  </si>
+  <si>
+    <t>0.2222,0.0157,0.7322,0.0013</t>
+  </si>
+  <si>
+    <t>0.9271,0.1162,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9822,0.0151,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.9846,0.0103,0.0013,0.0004</t>
+  </si>
+  <si>
+    <t>0.9433,0.0607,0.0008,0.0007</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,1.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9253,0.0551,0.0097,0.0009</t>
+  </si>
+  <si>
+    <t>0.0001,0.0126,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.4050,0.9993,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.0027,0.9986,0.0005</t>
+  </si>
+  <si>
+    <t>0.0146,0.0171,0.9676,0.0014</t>
+  </si>
+  <si>
+    <t>0.0011,0.0218,0.9941,0.0006</t>
+  </si>
+  <si>
+    <t>0.0002,0.0010,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0025,0.0049,0.9943,0.0004</t>
+  </si>
+  <si>
+    <t>0.0177,0.0324,0.9621,0.0023</t>
+  </si>
+  <si>
+    <t>0.0247,0.0044,0.9670,0.0021</t>
+  </si>
+  <si>
+    <t>0.0187,0.9568,0.0394,0.0082</t>
+  </si>
+  <si>
+    <t>0.2829,0.4292,0.1063,0.0025</t>
+  </si>
+  <si>
+    <t>0.0086,0.9849,0.0099,0.0005</t>
+  </si>
+  <si>
+    <t>0.3575,0.2007,0.1433,0.0006</t>
+  </si>
+  <si>
+    <t>0.6058,0.0639,0.1664,0.0058</t>
+  </si>
+  <si>
+    <t>0.6392,0.0815,0.1617,0.0072</t>
+  </si>
+  <si>
+    <t>0.0060,0.9937,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.0010,0.9986,0.0023,0.0000</t>
+  </si>
+  <si>
+    <t>0.0304,0.9796,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.9066,0.1432,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0742,0.9494,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.0109,0.9859,0.0021,0.0012</t>
+  </si>
+  <si>
+    <t>0.9267,0.0347,0.0127,0.0006</t>
+  </si>
+  <si>
+    <t>0.5630,0.1068,0.0061,0.0430</t>
+  </si>
+  <si>
+    <t>0.0243,0.9602,0.0077,0.0086</t>
+  </si>
+  <si>
+    <t>0.9495,0.0046,0.0274,0.0009</t>
+  </si>
+  <si>
+    <t>0.0184,0.0038,0.9739,0.0048</t>
+  </si>
+  <si>
+    <t>0.0072,0.7644,0.4748,0.0040</t>
+  </si>
+  <si>
+    <t>0.0114,0.4170,0.9056,0.0020</t>
+  </si>
+  <si>
+    <t>0.5897,0.0050,0.4219,0.0009</t>
+  </si>
+  <si>
+    <t>0.0010,0.8983,0.8119,0.0001</t>
+  </si>
+  <si>
+    <t>0.9934,0.0063,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.7795,0.3198,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.9880,0.0184,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9683,0.0428,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9936,0.0047,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9938,0.0040,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9977,0.0009,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0052,0.9991,0.0006</t>
+  </si>
+  <si>
+    <t>0.0178,0.9656,0.0249,0.0012</t>
+  </si>
+  <si>
+    <t>0.7527,0.0113,0.1525,0.0019</t>
+  </si>
+  <si>
+    <t>0.0011,0.0011,0.9989,0.0000</t>
+  </si>
+  <si>
+    <t>0.0019,0.0084,0.9942,0.0006</t>
+  </si>
+  <si>
+    <t>0.0030,0.1301,0.9759,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0006,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0042,0.0130,0.9841,0.0010</t>
+  </si>
+  <si>
+    <t>0.0003,0.0008,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0024,0.0047,0.9944,0.0002</t>
+  </si>
+  <si>
+    <t>0.0110,0.1065,0.9445,0.0024</t>
+  </si>
+  <si>
+    <t>0.3615,0.0350,0.4647,0.0036</t>
+  </si>
+  <si>
+    <t>0.8838,0.0021,0.1224,0.0011</t>
+  </si>
+  <si>
+    <t>0.8775,0.0905,0.0011,0.0007</t>
+  </si>
+  <si>
+    <t>0.9975,0.0025,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9974,0.0023,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9925,0.0052,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9942,0.0052,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9708,0.0428,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9960,0.0030,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.1568,0.1276,0.5169,0.0027</t>
+  </si>
+  <si>
+    <t>0.0006,0.0309,0.9986,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.4979,0.9688,0.0003</t>
+  </si>
+  <si>
+    <t>0.0113,0.5815,0.5076,0.0090</t>
+  </si>
+  <si>
+    <t>0.0019,0.0085,0.9961,0.0003</t>
+  </si>
+  <si>
+    <t>0.2488,0.0110,0.6295,0.0474</t>
+  </si>
+  <si>
+    <t>0.0203,0.0011,0.9675,0.0029</t>
+  </si>
+  <si>
+    <t>0.0776,0.0134,0.8799,0.0038</t>
+  </si>
+  <si>
+    <t>0.7282,0.0001,0.0012,0.3330</t>
+  </si>
+  <si>
+    <t>0.0106,0.2129,0.0009,0.9740</t>
+  </si>
+  <si>
+    <t>0.0095,0.0003,0.0005,0.9961</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.6652,0.0083,0.0004,0.1186</t>
   </si>
 </sst>
 </file>
@@ -1947,7 +1944,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1961,7 +1958,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1975,7 +1972,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1989,7 +1986,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2003,7 +2000,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2017,7 +2014,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2031,7 +2028,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2045,7 +2042,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2059,7 +2056,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2073,7 +2070,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2087,7 +2084,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2101,7 +2098,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2112,10 +2109,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2129,7 +2126,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2143,7 +2140,7 @@
         <v>259</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2157,7 +2154,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2171,7 +2168,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2185,7 +2182,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2199,7 +2196,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2213,7 +2210,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2227,7 +2224,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2241,7 +2238,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2252,10 +2249,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2266,10 +2263,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2283,7 +2280,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2297,7 +2294,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2311,7 +2308,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2325,7 +2322,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2339,7 +2336,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2353,7 +2350,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2367,7 +2364,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2381,7 +2378,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2395,7 +2392,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2409,7 +2406,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2423,7 +2420,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2437,7 +2434,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2451,7 +2448,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2462,10 +2459,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2476,10 +2473,10 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2490,10 +2487,10 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2507,7 +2504,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2521,7 +2518,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2535,7 +2532,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2549,7 +2546,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2560,10 +2557,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2577,7 +2574,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2591,7 +2588,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2605,7 +2602,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>282</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2619,7 +2616,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2630,10 +2627,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2647,7 +2644,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2661,7 +2658,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2675,7 +2672,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2689,7 +2686,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2703,7 +2700,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2717,7 +2714,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2731,7 +2728,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2745,7 +2742,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2759,7 +2756,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2773,7 +2770,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2787,7 +2784,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2801,7 +2798,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2815,7 +2812,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2829,7 +2826,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2843,7 +2840,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2857,7 +2854,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2871,7 +2868,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2885,7 +2882,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2899,7 +2896,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2913,7 +2910,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2927,7 +2924,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2941,7 +2938,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2952,10 +2949,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2969,7 +2966,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2980,10 +2977,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2997,7 +2994,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3011,7 +3008,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3025,7 +3022,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3039,7 +3036,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3053,7 +3050,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3067,7 +3064,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3081,7 +3078,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3095,7 +3092,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3109,7 +3106,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3120,10 +3117,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3134,10 +3131,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3151,7 +3148,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3165,7 +3162,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3179,7 +3176,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3193,7 +3190,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3207,7 +3204,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3221,7 +3218,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3235,7 +3232,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3249,7 +3246,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3263,7 +3260,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3277,7 +3274,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3291,7 +3288,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3305,7 +3302,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3319,7 +3316,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3333,7 +3330,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>269</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3361,7 +3358,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3375,7 +3372,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3389,7 +3386,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3403,7 +3400,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3417,7 +3414,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3431,7 +3428,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3445,7 +3442,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>370</v>
+        <v>299</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3459,7 +3456,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3473,7 +3470,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3487,7 +3484,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3501,7 +3498,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3515,7 +3512,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3529,7 +3526,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3540,10 +3537,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D116" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3557,7 +3554,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3571,7 +3568,7 @@
         <v>262</v>
       </c>
       <c r="D118" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3582,10 +3579,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D119" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3599,7 +3596,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3613,7 +3610,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>382</v>
+        <v>284</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3627,7 +3624,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>383</v>
+        <v>314</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3680,7 +3677,7 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D126" t="s">
         <v>387</v>
@@ -3694,7 +3691,7 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
         <v>388</v>
@@ -3834,7 +3831,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
         <v>398</v>
@@ -3890,7 +3887,7 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D141" t="s">
         <v>402</v>
@@ -3918,7 +3915,7 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D143" t="s">
         <v>404</v>
@@ -3932,7 +3929,7 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
         <v>405</v>
@@ -4072,7 +4069,7 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D154" t="s">
         <v>415</v>
@@ -4198,7 +4195,7 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D163" t="s">
         <v>424</v>
@@ -4327,7 +4324,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>272</v>
+        <v>433</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4341,7 +4338,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4355,7 +4352,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4366,10 +4363,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D175" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4380,10 +4377,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4394,10 +4391,10 @@
         <v>259</v>
       </c>
       <c r="C177" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4411,7 +4408,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4425,7 +4422,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4439,7 +4436,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4453,7 +4450,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4467,7 +4464,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4481,7 +4478,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4495,7 +4492,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4509,7 +4506,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4523,7 +4520,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4537,7 +4534,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4551,7 +4548,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4565,7 +4562,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4579,7 +4576,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4593,7 +4590,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4604,10 +4601,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D192" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4618,10 +4615,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D193" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4632,10 +4629,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4646,10 +4643,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D195" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4663,7 +4660,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4677,7 +4674,7 @@
         <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4691,7 +4688,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4705,7 +4702,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4719,7 +4716,7 @@
         <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4733,7 +4730,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4747,7 +4744,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4761,7 +4758,7 @@
         <v>262</v>
       </c>
       <c r="D203" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4775,7 +4772,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4789,7 +4786,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4803,7 +4800,7 @@
         <v>262</v>
       </c>
       <c r="D206" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4817,7 +4814,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4831,7 +4828,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4842,10 +4839,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D209" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4856,10 +4853,10 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4873,7 +4870,7 @@
         <v>259</v>
       </c>
       <c r="D211" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4887,7 +4884,7 @@
         <v>263</v>
       </c>
       <c r="D212" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4901,7 +4898,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>473</v>
+        <v>272</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -5097,7 +5094,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5111,7 +5108,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5125,7 +5122,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5139,7 +5136,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5153,7 +5150,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5164,10 +5161,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D232" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5181,7 +5178,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5195,7 +5192,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5209,7 +5206,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5223,7 +5220,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5237,7 +5234,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>496</v>
+        <v>367</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5318,7 +5315,7 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
         <v>502</v>
@@ -5360,7 +5357,7 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D246" t="s">
         <v>505</v>
@@ -5430,7 +5427,7 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D251" t="s">
         <v>510</v>
@@ -5489,7 +5486,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5503,7 +5500,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
   </sheetData>
